--- a/apps/frontend-next/_docs/testing/e2e-test-cases.xlsx
+++ b/apps/frontend-next/_docs/testing/e2e-test-cases.xlsx
@@ -22,7 +22,7 @@
     <t>生成日時</t>
   </si>
   <si>
-    <t>2026/9/21 11:11:08</t>
+    <t>2026/9/21 11:23:14</t>
   </si>
   <si>
     <t>最終実行</t>
